--- a/data/sots_overrides.xlsx
+++ b/data/sots_overrides.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -624,6 +624,18 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Manuel Locatelli</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://sortitoutsi.net/football-manager-2026/person/43167354/manuel-locatelli</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/sots_overrides.xlsx
+++ b/data/sots_overrides.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -636,6 +636,198 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Antoine Sekongo</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>https://sortitoutsi.net/football-manager-2026/person/2000279641/antoine-sekongo</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Baptiste Mouazan</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://sortitoutsi.net/football-manager-2026/person/49050068/baptiste-mouazan</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Emersonn</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>https://sortitoutsi.net/football-manager-2026/person/19409149/emersonn</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Emiliano Filippis</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>https://sortitoutsi.net/football-manager-2026/person/2000047967/emiliano-filippis</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ewen Jaouen</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://sortitoutsi.net/football-manager-2026/person/2000183134/ewen-jaouen</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Gessime Yassine</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>https://sortitoutsi.net/football-manager-2026/person/2000333625/gessime-yassine</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ibrahim El Kadiri</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>https://sortitoutsi.net/football-manager-2026/person/37075213/ibrahim-el-kadiri</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Jeremy Monga</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>https://sortitoutsi.net/football-manager-2026/person/2000474101/jeremy-monga</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Joseph Kalulu</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>https://sortitoutsi.net/football-manager-2026/person/2000402614/joseph-kalulu</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Lucas Stassin</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>https://sortitoutsi.net/football-manager-2026/person/2000022188/lucas-stassin</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Martial Tia</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>https://sortitoutsi.net/football-manager-2026/person/12095307/martial-tia</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Triston Rowe</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>https://sortitoutsi.net/football-manager-2026/person/2000283795/triston-rowe</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Víctor Muñoz</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>https://sortitoutsi.net/football-manager-2026/person/2000126470/victor-munoz</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Wisdom Amey</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>https://sortitoutsi.net/football-manager-2026/person/2000097938/wisdom-amey</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Yann Gboho</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>https://sortitoutsi.net/football-manager-2026/person/49038961/yann-gboho</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Yassine Benhattab</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>https://sortitoutsi.net/football-manager-2026/person/49056530/yassine-benhattab</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
